--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -53,12 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
   </si>
   <si>
     <t>В0583ВТ</t>
@@ -110,8 +104,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -197,11 +192,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -209,9 +205,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -565,20 +561,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46149</v>
       </c>
       <c r="B2">
         <v>1148</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
       </c>
       <c r="F2">
         <v>20</v>
@@ -596,7 +592,7 @@
         <v>30.6</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -606,20 +602,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="2">
+        <v>46153</v>
       </c>
       <c r="B3">
         <v>1148</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
       </c>
       <c r="F3">
         <v>19.41</v>
@@ -637,7 +633,7 @@
         <v>16.11</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -646,115 +642,110 @@
         <v>204497</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="F4">
-        <v>39.41</v>
-      </c>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="C7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>28</v>
+      <c r="A8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="6">
+        <v>20</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="E8" s="6">
+        <v>30</v>
+      </c>
+      <c r="F8" s="6">
+        <v>30.6</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="5">
-        <v>20</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="A9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="6">
+        <v>19.41</v>
+      </c>
+      <c r="C9" s="6">
         <v>1</v>
       </c>
-      <c r="D9" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="E9" s="5">
-        <v>30</v>
-      </c>
-      <c r="F9" s="5">
-        <v>30.6</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0.6</v>
+      <c r="D9" s="6">
+        <v>0.8202</v>
+      </c>
+      <c r="E9" s="6">
+        <v>15.92</v>
+      </c>
+      <c r="F9" s="6">
+        <v>16.11</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.19</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="5">
-        <v>19.41</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0.8202</v>
-      </c>
-      <c r="E10" s="5">
-        <v>15.92</v>
-      </c>
-      <c r="F10" s="5">
-        <v>16.11</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="7">
+      <c r="A10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="8">
         <v>39.41</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C10" s="8">
         <v>2</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
         <v>45.92</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F10" s="8">
         <v>46.71</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G10" s="8">
         <v>0.79</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -146,7 +146,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,12 +156,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -212,17 +206,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,49 +46,25 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>В0583ВТ</t>
   </si>
   <si>
     <t>ТубаЗвездица</t>
   </si>
   <si>
-    <t>В0583ВТ</t>
+    <t>78970155027721806</t>
   </si>
   <si>
     <t>78970155027722747</t>
   </si>
   <si>
-    <t>78970155027721806</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>09:51:00</t>
-  </si>
-  <si>
-    <t>12:11:00</t>
-  </si>
-  <si>
-    <t>3232051576 3232051576</t>
-  </si>
-  <si>
-    <t>3232576517 3232576517</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ЗВЕЗДИЦА</t>
@@ -511,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,17 +493,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,195 +534,183 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H2">
+        <v>15.4</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J2">
+        <v>15.7</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3">
+        <v>19.99</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H3">
+        <v>30.78</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J3">
+        <v>31.38</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46160</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H4">
+        <v>30.6</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J4">
+        <v>31.2</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
+      <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>1.52</v>
-      </c>
-      <c r="I2" s="1">
-        <v>30.4</v>
-      </c>
-      <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>31</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="7">
+        <v>49.99</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.5359</v>
+      </c>
+      <c r="E9" s="7">
+        <v>76.78</v>
+      </c>
+      <c r="F9" s="7">
+        <v>78.28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46171</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>22.93</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>0.76</v>
-      </c>
-      <c r="I3" s="1">
-        <v>17.43</v>
-      </c>
-      <c r="J3">
-        <v>0.77</v>
-      </c>
-      <c r="K3" s="1">
-        <v>17.66</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="7">
-        <v>22.93</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.7601</v>
-      </c>
-      <c r="E8" s="7">
-        <v>17.43</v>
-      </c>
-      <c r="F8" s="7">
-        <v>17.66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7">
-        <v>20</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="E9" s="7">
-        <v>30.4</v>
-      </c>
-      <c r="F9" s="7">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="B10" s="10">
-        <v>42.93</v>
+        <v>49.99</v>
       </c>
       <c r="C10" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="10">
-        <v>47.83</v>
+        <v>76.78</v>
       </c>
       <c r="F10" s="10">
-        <v>48.66</v>
+        <v>78.28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Порт</t>
   </si>
   <si>
@@ -65,6 +71,15 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>09:27</t>
+  </si>
+  <si>
+    <t>09:28</t>
+  </si>
+  <si>
+    <t>08:51</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ЗВЕЗДИЦА</t>
@@ -484,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -497,10 +512,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -534,22 +551,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -566,25 +589,31 @@
       <c r="J2">
         <v>15.7</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
+      <c r="M2">
+        <v>213384</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46174</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>19.99</v>
@@ -601,25 +630,31 @@
       <c r="J3">
         <v>31.38</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3">
         <v>0</v>
       </c>
+      <c r="M3">
+        <v>213386</v>
+      </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46183</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>20</v>
@@ -636,13 +671,19 @@
       <c r="J4">
         <v>31.2</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4">
         <v>0</v>
       </c>
+      <c r="M4">
+        <v>217092</v>
+      </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -650,18 +691,18 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>7</v>
@@ -670,9 +711,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="7">
         <v>49.99</v>
@@ -690,9 +731,9 @@
         <v>78.28</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B10" s="10">
         <v>49.99</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -49,12 +49,6 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Порт</t>
   </si>
   <si>
@@ -70,16 +64,16 @@
     <t>78970155027722747</t>
   </si>
   <si>
+    <t>E GAS LPG</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>09:27</t>
-  </si>
-  <si>
-    <t>09:28</t>
-  </si>
-  <si>
-    <t>08:51</t>
+    <t>2026-06-22 12:11:50</t>
+  </si>
+  <si>
+    <t>2026-06-24 09:19:11</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ЗВЕЗДИЦА</t>
@@ -499,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -512,12 +506,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -551,207 +543,168 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>24.48</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>15.91</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>16.16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46174</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H3">
+        <v>29.6</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J3">
+        <v>30.2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H2">
-        <v>15.4</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J2">
-        <v>15.7</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>213384</v>
+      <c r="B8" s="7">
+        <v>24.48</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.6499</v>
+      </c>
+      <c r="E8" s="7">
+        <v>15.91</v>
+      </c>
+      <c r="F8" s="7">
+        <v>16.16</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46174</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>19.99</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H3">
-        <v>30.78</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J3">
-        <v>31.38</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="B9" s="7">
         <v>20</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>213386</v>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.48</v>
+      </c>
+      <c r="E9" s="7">
+        <v>29.6</v>
+      </c>
+      <c r="F9" s="7">
+        <v>30.2</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46183</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H4">
-        <v>30.6</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J4">
-        <v>31.2</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>217092</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="5" t="s">
+    <row r="10" spans="1:11">
+      <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="7">
-        <v>49.99</v>
-      </c>
-      <c r="C9" s="7">
-        <v>3</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.5359</v>
-      </c>
-      <c r="E9" s="7">
-        <v>76.78</v>
-      </c>
-      <c r="F9" s="7">
-        <v>78.28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="9" t="s">
-        <v>27</v>
-      </c>
       <c r="B10" s="10">
-        <v>49.99</v>
+        <v>44.48</v>
       </c>
       <c r="C10" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="10">
-        <v>76.78</v>
+        <v>45.51</v>
       </c>
       <c r="F10" s="10">
-        <v>78.28</v>
+        <v>46.36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,13 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
   </si>
   <si>
     <t>В0583ВТ</t>
@@ -70,10 +79,31 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-22 12:11:50</t>
-  </si>
-  <si>
-    <t>2026-06-24 09:19:11</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>12:11:00</t>
+  </si>
+  <si>
+    <t>09:19:00</t>
+  </si>
+  <si>
+    <t>09:05:00</t>
+  </si>
+  <si>
+    <t>09:06:00</t>
+  </si>
+  <si>
+    <t>3233721271 3233721271</t>
+  </si>
+  <si>
+    <t>3233811206 3233811206</t>
+  </si>
+  <si>
+    <t>3234100056 3234100056</t>
+  </si>
+  <si>
+    <t>3234101420 3234101420</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ЗВЕЗДИЦА</t>
@@ -493,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -502,14 +532,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,168 +576,283 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46195</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>24.48</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
         <v>0.65</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>15.91</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>0.66</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>16.16</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>119457</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46197</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
         <v>1.48</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>29.6</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.51</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>30.2</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4">
+        <v>1.47</v>
+      </c>
+      <c r="I4" s="1">
+        <v>29.4</v>
+      </c>
+      <c r="J4">
+        <v>1.5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="4" t="s">
+      <c r="F5">
+        <v>21.27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5">
+        <v>0.65</v>
+      </c>
+      <c r="I5" s="1">
+        <v>13.83</v>
+      </c>
+      <c r="J5">
+        <v>0.66</v>
+      </c>
+      <c r="K5" s="1">
+        <v>14.04</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5">
+        <v>119677</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7">
+        <v>45.75</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.6501</v>
+      </c>
+      <c r="E10" s="7">
+        <v>29.74</v>
+      </c>
+      <c r="F10" s="7">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="7">
-        <v>24.48</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.6499</v>
-      </c>
-      <c r="E8" s="7">
-        <v>15.91</v>
-      </c>
-      <c r="F8" s="7">
-        <v>16.16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="7">
-        <v>20</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.48</v>
-      </c>
-      <c r="E9" s="7">
-        <v>29.6</v>
-      </c>
-      <c r="F9" s="7">
-        <v>30.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="10">
-        <v>44.48</v>
-      </c>
-      <c r="C10" s="10">
+      <c r="B11" s="7">
+        <v>40</v>
+      </c>
+      <c r="C11" s="7">
         <v>2</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>45.51</v>
-      </c>
-      <c r="F10" s="10">
-        <v>46.36</v>
+      <c r="D11" s="8">
+        <v>1.475</v>
+      </c>
+      <c r="E11" s="7">
+        <v>59</v>
+      </c>
+      <c r="F11" s="7">
+        <v>60.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="10">
+        <v>85.75</v>
+      </c>
+      <c r="C12" s="10">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="10">
+        <v>88.73999999999999</v>
+      </c>
+      <c r="F12" s="10">
+        <v>90.40000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>В0583ВТ</t>
@@ -79,31 +76,16 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>12:11:00</t>
-  </si>
-  <si>
-    <t>09:19:00</t>
-  </si>
-  <si>
-    <t>09:05:00</t>
-  </si>
-  <si>
-    <t>09:06:00</t>
-  </si>
-  <si>
-    <t>3233721271 3233721271</t>
-  </si>
-  <si>
-    <t>3233811206 3233811206</t>
-  </si>
-  <si>
-    <t>3234100056 3234100056</t>
-  </si>
-  <si>
-    <t>3234101420 3234101420</t>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>09:06</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ЗВЕЗДИЦА</t>
@@ -523,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -532,17 +514,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -582,189 +563,174 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46195</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>24.48</v>
       </c>
-      <c r="G2" t="s">
-        <v>21</v>
+      <c r="G2" s="1">
+        <v>0.65</v>
       </c>
       <c r="H2">
-        <v>0.65</v>
+        <v>15.91</v>
       </c>
       <c r="I2" s="1">
-        <v>15.91</v>
+        <v>0.66</v>
       </c>
       <c r="J2">
-        <v>0.66</v>
-      </c>
-      <c r="K2" s="1">
         <v>16.16</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>119457</v>
       </c>
       <c r="M2">
-        <v>119457</v>
-      </c>
-      <c r="N2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>222384</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46197</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H3">
+        <v>29.6</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J3">
+        <v>30.2</v>
+      </c>
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="H3">
-        <v>1.48</v>
-      </c>
-      <c r="I3" s="1">
-        <v>29.6</v>
-      </c>
-      <c r="J3">
-        <v>1.51</v>
-      </c>
-      <c r="K3" s="1">
-        <v>30.2</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>223280</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46203</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4">
         <v>20</v>
       </c>
-      <c r="G4" t="s">
-        <v>21</v>
+      <c r="G4" s="1">
+        <v>1.47</v>
       </c>
       <c r="H4">
-        <v>1.47</v>
+        <v>29.4</v>
       </c>
       <c r="I4" s="1">
-        <v>29.4</v>
+        <v>1.5</v>
       </c>
       <c r="J4">
-        <v>1.5</v>
-      </c>
-      <c r="K4" s="1">
         <v>30</v>
       </c>
-      <c r="L4" t="s">
-        <v>24</v>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>225801</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46203</v>
       </c>
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5">
         <v>21.27</v>
       </c>
-      <c r="G5" t="s">
-        <v>21</v>
+      <c r="G5" s="1">
+        <v>0.65</v>
       </c>
       <c r="H5">
-        <v>0.65</v>
+        <v>13.83</v>
       </c>
       <c r="I5" s="1">
-        <v>13.83</v>
+        <v>0.66</v>
       </c>
       <c r="J5">
-        <v>0.66</v>
-      </c>
-      <c r="K5" s="1">
         <v>14.04</v>
       </c>
-      <c r="L5" t="s">
-        <v>25</v>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5">
+        <v>119677</v>
       </c>
       <c r="M5">
-        <v>119677</v>
-      </c>
-      <c r="N5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>225803</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -772,29 +738,29 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:13">
       <c r="A9" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="7">
         <v>45.75</v>
@@ -812,9 +778,9 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>40</v>
@@ -832,9 +798,9 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:13">
       <c r="A12" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B12" s="10">
         <v>85.75</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,19 +55,40 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>ТубаЗвездица</t>
   </si>
   <si>
     <t>В0583ВТ</t>
   </si>
   <si>
+    <t>78970155027722747</t>
+  </si>
+  <si>
     <t>78970155027721806</t>
   </si>
   <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-07-06 10:25:05</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>08:57:00</t>
+  </si>
+  <si>
+    <t>3235235182 3235235182</t>
+  </si>
+  <si>
+    <t>3235235386 3235235386</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ЗВЕЗДИЦА</t>
@@ -484,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -493,15 +517,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -538,116 +564,192 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46209</v>
+        <v>46226</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
+        <v>1.51</v>
+      </c>
+      <c r="I2" s="1">
+        <v>30.2</v>
+      </c>
+      <c r="J2">
+        <v>1.54</v>
+      </c>
+      <c r="K2" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>25.41</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H2">
-        <v>15.75</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>23.41</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
         <v>0.63</v>
       </c>
-      <c r="J2">
-        <v>16.01</v>
-      </c>
-      <c r="K2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2">
-        <v>119925</v>
+      <c r="I3" s="1">
+        <v>14.75</v>
+      </c>
+      <c r="J3">
+        <v>0.64</v>
+      </c>
+      <c r="K3" s="1">
+        <v>14.98</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
+        <v>12018</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row r="7" spans="1:14">
+      <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="7">
+        <v>23.41</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.6301</v>
+      </c>
+      <c r="E8" s="7">
+        <v>14.75</v>
+      </c>
+      <c r="F8" s="7">
+        <v>14.98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B9" s="7">
         <v>20</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.51</v>
+      </c>
+      <c r="E9" s="7">
+        <v>30.2</v>
+      </c>
+      <c r="F9" s="7">
+        <v>30.8</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="7">
-        <v>25.41</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.6198</v>
-      </c>
-      <c r="E7" s="7">
-        <v>15.75</v>
-      </c>
-      <c r="F7" s="7">
-        <v>16.01</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="10">
-        <v>25.41</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="10">
-        <v>15.75</v>
-      </c>
-      <c r="F8" s="10">
-        <v>16.01</v>
+    <row r="10" spans="1:14">
+      <c r="A10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="10">
+        <v>43.41</v>
+      </c>
+      <c r="C10" s="10">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>44.95</v>
+      </c>
+      <c r="F10" s="10">
+        <v>45.78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -116,7 +116,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -700,7 +700,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="8">
-        <v>0.6301</v>
+        <v>0.630073</v>
       </c>
       <c r="E8" s="7">
         <v>14.75</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -508,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -521,13 +524,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,98 +573,107 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46226</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2">
+        <v>1.401</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.51</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>30.2</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1.54</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>30.8</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>23</v>
+      <c r="O2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46226</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>23.41</v>
+        <v>23.406</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.63</v>
       </c>
-      <c r="I3" s="1">
-        <v>14.75</v>
-      </c>
       <c r="J3">
+        <v>14.74578</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.64</v>
       </c>
-      <c r="K3" s="1">
-        <v>14.98</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>14.97984</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
         <v>12018</v>
       </c>
-      <c r="N3" t="s">
-        <v>24</v>
+      <c r="O3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -669,38 +681,38 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="7">
-        <v>23.41</v>
+        <v>23.406</v>
       </c>
       <c r="C8" s="7">
         <v>1</v>
       </c>
       <c r="D8" s="8">
-        <v>0.630073</v>
+        <v>0.63</v>
       </c>
       <c r="E8" s="7">
         <v>14.75</v>
@@ -709,9 +721,9 @@
         <v>14.98</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="7">
         <v>20</v>
@@ -729,12 +741,12 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="10">
-        <v>43.41</v>
+        <v>43.406</v>
       </c>
       <c r="C10" s="10">
         <v>2</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -117,9 +114,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -213,10 +210,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -524,13 +521,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -573,107 +570,98 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46226</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
       <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
+        <v>1.51</v>
+      </c>
+      <c r="I2" s="1">
+        <v>30.2</v>
+      </c>
+      <c r="J2">
+        <v>1.54</v>
+      </c>
+      <c r="K2" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="H2">
-        <v>1.401</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J2">
-        <v>30.2</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L2" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
         <v>23</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46226</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>23.406</v>
       </c>
       <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
+        <v>0.63</v>
+      </c>
+      <c r="I3" s="1">
+        <v>14.746</v>
+      </c>
+      <c r="J3">
+        <v>0.64</v>
+      </c>
+      <c r="K3" s="1">
+        <v>14.98</v>
+      </c>
+      <c r="L3" t="s">
         <v>22</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J3">
-        <v>14.74578</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L3" s="1">
-        <v>14.97984</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3">
+      <c r="M3">
         <v>12018</v>
       </c>
-      <c r="O3" t="s">
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -681,69 +669,69 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="7">
         <v>23.406</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>1</v>
       </c>
       <c r="D8" s="8">
         <v>0.63</v>
       </c>
-      <c r="E8" s="7">
-        <v>14.75</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E8" s="8">
+        <v>14.746</v>
+      </c>
+      <c r="F8" s="8">
         <v>14.98</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7">
         <v>20</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>1</v>
       </c>
       <c r="D9" s="8">
         <v>1.51</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <v>30.2</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <v>30.8</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="10">
         <v>43.406</v>
@@ -753,7 +741,7 @@
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="10">
-        <v>44.95</v>
+        <v>44.946</v>
       </c>
       <c r="F10" s="10">
         <v>45.78</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,37 +55,25 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>ТубаЗвездица</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Евkсиноград</t>
   </si>
   <si>
     <t>В0583ВТ</t>
   </si>
   <si>
-    <t>78970155027722747</t>
-  </si>
-  <si>
     <t>78970155027721806</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>08:57:00</t>
-  </si>
-  <si>
-    <t>3235235182 3235235182</t>
-  </si>
-  <si>
-    <t>3235235386 3235235386</t>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>16:52</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ЗВЕЗДИЦА</t>
@@ -114,9 +99,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -210,10 +195,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -517,17 +502,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,101 +551,92 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46239</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46226</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
       <c r="F2">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
+        <v>24.818</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.65</v>
       </c>
       <c r="H2">
-        <v>1.51</v>
+        <v>16.132</v>
       </c>
       <c r="I2" s="1">
-        <v>30.2</v>
+        <v>0.66</v>
       </c>
       <c r="J2">
-        <v>1.54</v>
-      </c>
-      <c r="K2" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
+        <v>16.38</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2">
+        <v>120480</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
+        <v>242429</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46226</v>
+        <v>46242</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
       <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>16.652</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3">
+        <v>10.824</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3">
+        <v>10.99</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3">
+        <v>12064</v>
+      </c>
+      <c r="M3">
+        <v>236290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="F3">
-        <v>23.406</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>0.63</v>
-      </c>
-      <c r="I3" s="1">
-        <v>14.746</v>
-      </c>
-      <c r="J3">
-        <v>0.64</v>
-      </c>
-      <c r="K3" s="1">
-        <v>14.98</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
-        <v>12018</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -669,82 +644,62 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B8" s="7">
-        <v>23.406</v>
-      </c>
-      <c r="C8" s="8">
-        <v>1</v>
+        <v>41.47</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2</v>
       </c>
       <c r="D8" s="8">
-        <v>0.63</v>
-      </c>
-      <c r="E8" s="8">
-        <v>14.746</v>
-      </c>
-      <c r="F8" s="8">
-        <v>14.98</v>
+        <v>0.65001</v>
+      </c>
+      <c r="E8" s="7">
+        <v>26.96</v>
+      </c>
+      <c r="F8" s="7">
+        <v>27.37</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7">
-        <v>20</v>
-      </c>
-      <c r="C9" s="8">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.51</v>
-      </c>
-      <c r="E9" s="8">
-        <v>30.2</v>
-      </c>
-      <c r="F9" s="8">
-        <v>30.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="10">
-        <v>43.406</v>
-      </c>
-      <c r="C10" s="10">
+    <row r="9" spans="1:13">
+      <c r="A9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="10">
+        <v>41.47</v>
+      </c>
+      <c r="C9" s="10">
         <v>2</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>44.946</v>
-      </c>
-      <c r="F10" s="10">
-        <v>45.78</v>
+      <c r="D9" s="8"/>
+      <c r="E9" s="10">
+        <v>26.96</v>
+      </c>
+      <c r="F9" s="10">
+        <v>27.37</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,25 +58,46 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Евkсиноград</t>
+    <t>1148 Варна пристанище</t>
   </si>
   <si>
     <t>В0583ВТ</t>
   </si>
   <si>
+    <t>ТубаЗвездица</t>
+  </si>
+  <si>
     <t>78970155027721806</t>
   </si>
   <si>
+    <t>78970155027722747</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>10:07</t>
-  </si>
-  <si>
-    <t>16:52</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:08:00</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>18:10:00</t>
+  </si>
+  <si>
+    <t>3236565200 3236565200</t>
+  </si>
+  <si>
+    <t>3236868816 3236868816</t>
+  </si>
+  <si>
+    <t>3236880228 3236880228</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ЗВЕЗДИЦА</t>
@@ -98,10 +122,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -181,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -195,10 +220,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -502,16 +529,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -551,160 +579,233 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46239</v>
+        <v>46252</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>24.818</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H2">
-        <v>16.132</v>
+        <v>25.7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.99</v>
       </c>
       <c r="I2" s="1">
+        <v>25.443</v>
+      </c>
+      <c r="J2" s="1">
         <v>0.66</v>
       </c>
-      <c r="J2">
-        <v>16.38</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2">
-        <v>120480</v>
+      <c r="K2" s="1">
+        <v>16.962</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
       </c>
       <c r="M2">
-        <v>242429</v>
+        <v>120905</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46242</v>
+        <v>46258</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.439</v>
+      </c>
+      <c r="I3" s="1">
+        <v>28.78</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="K3" s="1">
+        <v>31.4</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="F3">
-        <v>16.652</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H3">
-        <v>10.824</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>18.8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I4" s="1">
+        <v>18.612</v>
+      </c>
+      <c r="J4" s="1">
         <v>0.66</v>
       </c>
-      <c r="J3">
-        <v>10.99</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="K4" s="1">
+        <v>12.408</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
+        <v>120100</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L3">
-        <v>12064</v>
-      </c>
-      <c r="M3">
-        <v>236290</v>
+      <c r="B9" s="7">
+        <v>44.5</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="E9" s="7">
+        <v>44.06</v>
+      </c>
+      <c r="F9" s="7">
+        <v>29.37</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="B10" s="7">
+        <v>20</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1.439</v>
+      </c>
+      <c r="E10" s="7">
+        <v>28.78</v>
+      </c>
+      <c r="F10" s="7">
+        <v>31.4</v>
+      </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="7">
-        <v>41.47</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.65001</v>
-      </c>
-      <c r="E8" s="7">
-        <v>26.96</v>
-      </c>
-      <c r="F8" s="7">
-        <v>27.37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="10">
-        <v>41.47</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10">
-        <v>26.96</v>
-      </c>
-      <c r="F9" s="10">
-        <v>27.37</v>
+    <row r="11" spans="1:14">
+      <c r="A11" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="11">
+        <v>64.5</v>
+      </c>
+      <c r="C11" s="12">
+        <v>3</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="11">
+        <v>72.84</v>
+      </c>
+      <c r="F11" s="11">
+        <v>60.77</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ЗВЕЗДИЦА/КМЕТСТВО ЗВЕЗДИЦА.xlsx
@@ -606,10 +606,10 @@
         <v>21</v>
       </c>
       <c r="H2" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="1">
-        <v>25.443</v>
+        <v>16.705</v>
       </c>
       <c r="J2" s="1">
         <v>0.66</v>
@@ -650,10 +650,10 @@
         <v>21</v>
       </c>
       <c r="H3" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I3" s="1">
-        <v>28.78</v>
+        <v>30.8</v>
       </c>
       <c r="J3" s="1">
         <v>1.57</v>
@@ -694,10 +694,10 @@
         <v>21</v>
       </c>
       <c r="H4" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I4" s="1">
-        <v>18.612</v>
+        <v>12.22</v>
       </c>
       <c r="J4" s="1">
         <v>0.66</v>
@@ -756,10 +756,10 @@
         <v>2</v>
       </c>
       <c r="D9" s="9">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="E9" s="7">
-        <v>44.06</v>
+        <v>28.92</v>
       </c>
       <c r="F9" s="7">
         <v>29.37</v>
@@ -776,10 +776,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="9">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="E10" s="7">
-        <v>28.78</v>
+        <v>30.8</v>
       </c>
       <c r="F10" s="7">
         <v>31.4</v>
@@ -797,7 +797,7 @@
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="11">
-        <v>72.84</v>
+        <v>59.72</v>
       </c>
       <c r="F11" s="11">
         <v>60.77</v>
